--- a/drg/menaka dd/archi/calculations load/stair dead load calculation.xlsx
+++ b/drg/menaka dd/archi/calculations load/stair dead load calculation.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9808C79-FBA4-4E5E-876A-17486D035A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD05975E-79B7-4268-9A0D-34939EEDAC2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="300" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2820" yWindow="528" windowWidth="17280" windowHeight="11256" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WL(resting on beam and slab)" sheetId="1" r:id="rId1"/>
@@ -4001,8 +4001,8 @@
         <v>20/14.34</v>
       </c>
       <c r="D50" s="32">
-        <f>20/15.22</f>
-        <v>1.3140604467805519</v>
+        <f>20/20.3</f>
+        <v>0.98522167487684731</v>
       </c>
       <c r="E50" s="32"/>
       <c r="H50" s="56"/>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="C54" s="53">
         <f>ROUNDUP(((G54*12)+H54)*0.0254,3)</f>
-        <v>0.153</v>
+        <v>0.17200000000000001</v>
       </c>
       <c r="D54" s="32"/>
       <c r="E54" s="32"/>
@@ -4053,7 +4053,7 @@
         <v>0</v>
       </c>
       <c r="H54" s="30">
-        <v>6</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -4081,15 +4081,15 @@
       </c>
       <c r="C56" s="53">
         <f>ROUNDUP(((G56*12)+H56)*0.0254,3)</f>
-        <v>1.22</v>
+        <v>1.016</v>
       </c>
       <c r="D56" s="32"/>
       <c r="E56" s="32"/>
       <c r="G56" s="29">
+        <v>3</v>
+      </c>
+      <c r="H56" s="55">
         <v>4</v>
-      </c>
-      <c r="H56" s="55">
-        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="C59" s="4" t="str">
         <f>CONCATENATE("(",C54,"*",C55,"*",C57,")/{2*sqrt(",C54,"^2+",C55,"^2}")</f>
-        <v>(0.153*0.254*25)/{2*sqrt(0.153^2+0.254^2}</v>
+        <v>(0.172*0.254*25)/{2*sqrt(0.172^2+0.254^2}</v>
       </c>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="C60" s="17">
         <f>(0.5*C54*C55*C57)/(SQRT(C54^2+C55^2))</f>
-        <v>1.6382454557113664</v>
+        <v>1.780235121607266</v>
       </c>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
